--- a/dietaryindex_SCORING_ALGORITHM.xlsx
+++ b/dietaryindex_SCORING_ALGORITHM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11018"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Library/Mobile Documents/com~apple~CloudDocs/Desktop/Emory University - Ph.D./dietaryindex_package/dietaryindex/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Desktop/Emory University - Ph.D./dietaryindex_package/dietaryindex/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9B1BF9-C6BC-3140-B2AA-5E6954FFB5A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD082BF-0BB8-A645-9F63-D0CEAAAF16CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7980" yWindow="500" windowWidth="25960" windowHeight="19420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="500" windowWidth="33460" windowHeight="19420" firstSheet="1" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HEI2020" sheetId="18" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="ACS 2020_V1" sheetId="13" r:id="rId11"/>
     <sheet name="ACS 2020_V2" sheetId="14" r:id="rId12"/>
     <sheet name="PHDI" sheetId="17" r:id="rId13"/>
+    <sheet name="DI-GM" sheetId="21" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1230" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1269" uniqueCount="522">
   <si>
     <t>Component</t>
   </si>
@@ -1755,12 +1756,103 @@
   <si>
     <t>1. https://www.ncbi.nlm.nih.gov/pmc/articles/PMC3738221/</t>
   </si>
+  <si>
+    <t>Beneficial to gut microbiota</t>
+  </si>
+  <si>
+    <t>Included Foods within the Component</t>
+  </si>
+  <si>
+    <t>Avocados</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Chickpea</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>Cranberries</t>
+  </si>
+  <si>
+    <t>Fermented dairy</t>
+  </si>
+  <si>
+    <t>Green tea</t>
+  </si>
+  <si>
+    <t>Soybean</t>
+  </si>
+  <si>
+    <t>Yogurt, cheese, kefir, sour cream,
+buttermilk</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Soy products–-Soy milk, Tofu</t>
+  </si>
+  <si>
+    <t>Grains defined as whole grains,
+containing the entire grain kernel—the
+bran, germ, and endosperm</t>
+  </si>
+  <si>
+    <t>Unfavorable to gut microbiota</t>
+  </si>
+  <si>
+    <t>High-fat diet (% energy)</t>
+  </si>
+  <si>
+    <t>Processed meat</t>
+  </si>
+  <si>
+    <t>Red meat</t>
+  </si>
+  <si>
+    <t>Frankfurters, sausages, corned beef, and
+luncheon meat that are made from beef,
+pork, or poultry</t>
+  </si>
+  <si>
+    <t>Beef, veal, pork, lamb, and game meat;
+excludes organ meat and cured meat</t>
+  </si>
+  <si>
+    <t>Refined grains</t>
+  </si>
+  <si>
+    <t>Refined grains that do not contain all of
+the components of the entire grain kernel</t>
+  </si>
+  <si>
+    <t>0 if consumption at or above 40% energy from fat, else 1</t>
+  </si>
+  <si>
+    <t>For each remaining component, a score of 0 if consumption at or above the sex-specific median, else 1</t>
+  </si>
+  <si>
+    <t>For each component, a score of 1 if consumption at or above the sex-specific median, else 0</t>
+  </si>
+  <si>
+    <t>Reference:</t>
+  </si>
+  <si>
+    <t>Kase BE, Liese AD, Zhang J, Murphy EA, Zhao L, Steck SE. The Development and Evaluation of a Literature-Based Dietary Index for Gut Microbiota. Nutrients. 2024;16(7):1045. Published 2024 Apr 3. doi:10.3390/nu16071045</t>
+  </si>
+  <si>
+    <t>Components of the Dietary Index for Gut Microbiota (DI-GM) identified based on the systematic review.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1934,6 +2026,25 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="15">
@@ -2317,7 +2428,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -2576,6 +2687,16 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2769,6 +2890,18 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3130,16 +3263,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="111" t="s">
         <v>445</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
+      <c r="B1" s="111"/>
+      <c r="C1" s="111"/>
+      <c r="D1" s="111"/>
+      <c r="E1" s="111"/>
+      <c r="F1" s="111"/>
+      <c r="G1" s="111"/>
+      <c r="H1" s="111"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3177,7 +3310,7 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="106" t="s">
+      <c r="H3" s="110" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3203,7 +3336,7 @@
       <c r="G4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="106"/>
+      <c r="H4" s="110"/>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -3227,7 +3360,7 @@
       <c r="G5" t="s">
         <v>34</v>
       </c>
-      <c r="H5" s="106"/>
+      <c r="H5" s="110"/>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -3251,7 +3384,7 @@
       <c r="G6" t="s">
         <v>35</v>
       </c>
-      <c r="H6" s="106"/>
+      <c r="H6" s="110"/>
     </row>
     <row r="7" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -3275,7 +3408,7 @@
       <c r="G7" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="106"/>
+      <c r="H7" s="110"/>
     </row>
     <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -3299,7 +3432,7 @@
       <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="106"/>
+      <c r="H8" s="110"/>
     </row>
     <row r="9" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -3323,7 +3456,7 @@
       <c r="G9" t="s">
         <v>39</v>
       </c>
-      <c r="H9" s="106"/>
+      <c r="H9" s="110"/>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -3347,7 +3480,7 @@
       <c r="G10" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="106"/>
+      <c r="H10" s="110"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -3371,7 +3504,7 @@
       <c r="G11" t="s">
         <v>33</v>
       </c>
-      <c r="H11" s="106"/>
+      <c r="H11" s="110"/>
     </row>
     <row r="12" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -3395,7 +3528,7 @@
       <c r="G12" t="s">
         <v>134</v>
       </c>
-      <c r="H12" s="106"/>
+      <c r="H12" s="110"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="11" t="s">
@@ -3407,7 +3540,7 @@
       <c r="E13" s="19"/>
       <c r="F13" s="19"/>
       <c r="G13" s="19"/>
-      <c r="H13" s="106"/>
+      <c r="H13" s="110"/>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -3431,7 +3564,7 @@
       <c r="G14" t="s">
         <v>43</v>
       </c>
-      <c r="H14" s="106"/>
+      <c r="H14" s="110"/>
     </row>
     <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -3455,7 +3588,7 @@
       <c r="G15" t="s">
         <v>40</v>
       </c>
-      <c r="H15" s="106"/>
+      <c r="H15" s="110"/>
     </row>
     <row r="16" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -3479,7 +3612,7 @@
       <c r="G16" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="106"/>
+      <c r="H16" s="110"/>
     </row>
     <row r="17" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
@@ -3503,7 +3636,7 @@
       <c r="G17" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="106"/>
+      <c r="H17" s="110"/>
     </row>
     <row r="18" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="9"/>
@@ -3530,16 +3663,16 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="26" x14ac:dyDescent="0.3">
-      <c r="A23" s="107" t="s">
+      <c r="A23" s="111" t="s">
         <v>446</v>
       </c>
-      <c r="B23" s="107"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="107"/>
+      <c r="B23" s="111"/>
+      <c r="C23" s="111"/>
+      <c r="D23" s="111"/>
+      <c r="E23" s="111"/>
+      <c r="F23" s="111"/>
+      <c r="G23" s="111"/>
+      <c r="H23" s="111"/>
     </row>
     <row r="24" spans="1:8" s="1" customFormat="1" ht="32" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3577,7 +3710,7 @@
       <c r="E25" s="13"/>
       <c r="F25" s="13"/>
       <c r="G25" s="13"/>
-      <c r="H25" s="106" t="s">
+      <c r="H25" s="110" t="s">
         <v>255</v>
       </c>
     </row>
@@ -3603,7 +3736,7 @@
       <c r="G26" t="s">
         <v>32</v>
       </c>
-      <c r="H26" s="106"/>
+      <c r="H26" s="110"/>
     </row>
     <row r="27" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
@@ -3627,7 +3760,7 @@
       <c r="G27" t="s">
         <v>34</v>
       </c>
-      <c r="H27" s="106"/>
+      <c r="H27" s="110"/>
     </row>
     <row r="28" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
@@ -3651,7 +3784,7 @@
       <c r="G28" t="s">
         <v>35</v>
       </c>
-      <c r="H28" s="106"/>
+      <c r="H28" s="110"/>
     </row>
     <row r="29" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
@@ -3675,7 +3808,7 @@
       <c r="G29" t="s">
         <v>36</v>
       </c>
-      <c r="H29" s="106"/>
+      <c r="H29" s="110"/>
     </row>
     <row r="30" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
@@ -3699,7 +3832,7 @@
       <c r="G30" t="s">
         <v>38</v>
       </c>
-      <c r="H30" s="106"/>
+      <c r="H30" s="110"/>
     </row>
     <row r="31" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
@@ -3723,7 +3856,7 @@
       <c r="G31" t="s">
         <v>39</v>
       </c>
-      <c r="H31" s="106"/>
+      <c r="H31" s="110"/>
     </row>
     <row r="32" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
@@ -3747,7 +3880,7 @@
       <c r="G32" t="s">
         <v>37</v>
       </c>
-      <c r="H32" s="106"/>
+      <c r="H32" s="110"/>
     </row>
     <row r="33" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
@@ -3771,7 +3904,7 @@
       <c r="G33" t="s">
         <v>33</v>
       </c>
-      <c r="H33" s="106"/>
+      <c r="H33" s="110"/>
     </row>
     <row r="34" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
@@ -3795,7 +3928,7 @@
       <c r="G34" t="s">
         <v>453</v>
       </c>
-      <c r="H34" s="106"/>
+      <c r="H34" s="110"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="11" t="s">
@@ -3807,7 +3940,7 @@
       <c r="E35" s="19"/>
       <c r="F35" s="19"/>
       <c r="G35" s="19"/>
-      <c r="H35" s="106"/>
+      <c r="H35" s="110"/>
     </row>
     <row r="36" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
@@ -3831,7 +3964,7 @@
       <c r="G36" t="s">
         <v>455</v>
       </c>
-      <c r="H36" s="106"/>
+      <c r="H36" s="110"/>
     </row>
     <row r="37" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
@@ -3855,7 +3988,7 @@
       <c r="G37" t="s">
         <v>456</v>
       </c>
-      <c r="H37" s="106"/>
+      <c r="H37" s="110"/>
     </row>
     <row r="38" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
@@ -3879,7 +4012,7 @@
       <c r="G38" t="s">
         <v>458</v>
       </c>
-      <c r="H38" s="106"/>
+      <c r="H38" s="110"/>
     </row>
     <row r="39" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
@@ -3903,7 +4036,7 @@
       <c r="G39" t="s">
         <v>460</v>
       </c>
-      <c r="H39" s="106"/>
+      <c r="H39" s="110"/>
     </row>
     <row r="40" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="9"/>
@@ -6458,31 +6591,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="25" customFormat="1" ht="30" x14ac:dyDescent="0.2">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="123" t="s">
         <v>310</v>
       </c>
       <c r="B1" s="77" t="s">
         <v>311</v>
       </c>
-      <c r="C1" s="122" t="s">
+      <c r="C1" s="126" t="s">
         <v>312</v>
       </c>
-      <c r="D1" s="123"/>
+      <c r="D1" s="127"/>
       <c r="E1" s="23"/>
       <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" s="25" customFormat="1" ht="31" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="120"/>
+      <c r="A2" s="124"/>
       <c r="B2" s="78" t="s">
         <v>313</v>
       </c>
-      <c r="C2" s="124"/>
-      <c r="D2" s="125"/>
+      <c r="C2" s="128"/>
+      <c r="D2" s="129"/>
       <c r="E2" s="23"/>
       <c r="F2" s="24"/>
     </row>
     <row r="3" spans="1:6" s="29" customFormat="1" ht="49" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="121"/>
+      <c r="A3" s="125"/>
       <c r="B3" s="26" t="s">
         <v>314</v>
       </c>
@@ -6500,13 +6633,13 @@
       </c>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="126" t="s">
+      <c r="A4" s="130" t="s">
         <v>319</v>
       </c>
-      <c r="B4" s="128" t="s">
+      <c r="B4" s="132" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="130">
+      <c r="C4" s="134">
         <v>0</v>
       </c>
       <c r="D4" s="30" t="s">
@@ -6518,9 +6651,9 @@
       <c r="F4" s="32"/>
     </row>
     <row r="5" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="127"/>
-      <c r="B5" s="129"/>
-      <c r="C5" s="131"/>
+      <c r="A5" s="131"/>
+      <c r="B5" s="133"/>
+      <c r="C5" s="135"/>
       <c r="D5" s="33" t="s">
         <v>323</v>
       </c>
@@ -6528,16 +6661,16 @@
       <c r="F5" s="32"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="113" t="s">
+      <c r="A6" s="117" t="s">
         <v>324</v>
       </c>
-      <c r="B6" s="115" t="s">
+      <c r="B6" s="119" t="s">
         <v>325</v>
       </c>
-      <c r="C6" s="113" t="s">
+      <c r="C6" s="117" t="s">
         <v>326</v>
       </c>
-      <c r="D6" s="117" t="s">
+      <c r="D6" s="121" t="s">
         <v>327</v>
       </c>
       <c r="E6" s="92" t="s">
@@ -6548,10 +6681,10 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="114"/>
-      <c r="B7" s="116"/>
-      <c r="C7" s="114"/>
-      <c r="D7" s="118"/>
+      <c r="A7" s="118"/>
+      <c r="B7" s="120"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="122"/>
       <c r="E7" s="94" t="s">
         <v>329</v>
       </c>
@@ -6560,10 +6693,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="114"/>
-      <c r="B8" s="116"/>
-      <c r="C8" s="114"/>
-      <c r="D8" s="118"/>
+      <c r="A8" s="118"/>
+      <c r="B8" s="120"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="122"/>
       <c r="E8" s="94" t="s">
         <v>330</v>
       </c>
@@ -6572,16 +6705,16 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="132" t="s">
+      <c r="A9" s="136" t="s">
         <v>331</v>
       </c>
-      <c r="B9" s="130" t="s">
+      <c r="B9" s="134" t="s">
         <v>332</v>
       </c>
-      <c r="C9" s="130">
-        <v>0</v>
-      </c>
-      <c r="D9" s="130" t="s">
+      <c r="C9" s="134">
+        <v>0</v>
+      </c>
+      <c r="D9" s="134" t="s">
         <v>333</v>
       </c>
       <c r="E9" s="34" t="s">
@@ -6592,10 +6725,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="133"/>
-      <c r="B10" s="134"/>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
+      <c r="A10" s="137"/>
+      <c r="B10" s="138"/>
+      <c r="C10" s="138"/>
+      <c r="D10" s="138"/>
       <c r="E10" s="36" t="s">
         <v>335</v>
       </c>
@@ -6604,10 +6737,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="133"/>
-      <c r="B11" s="134"/>
-      <c r="C11" s="134"/>
-      <c r="D11" s="134"/>
+      <c r="A11" s="137"/>
+      <c r="B11" s="138"/>
+      <c r="C11" s="138"/>
+      <c r="D11" s="138"/>
       <c r="E11" s="36" t="s">
         <v>336</v>
       </c>
@@ -6616,18 +6749,18 @@
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="133"/>
-      <c r="B12" s="134"/>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
+      <c r="A12" s="137"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
+      <c r="D12" s="138"/>
       <c r="E12" s="36"/>
       <c r="F12" s="37"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="133"/>
-      <c r="B13" s="134"/>
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
+      <c r="A13" s="137"/>
+      <c r="B13" s="138"/>
+      <c r="C13" s="138"/>
+      <c r="D13" s="138"/>
       <c r="E13" s="36" t="s">
         <v>337</v>
       </c>
@@ -6636,10 +6769,10 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="133"/>
-      <c r="B14" s="134"/>
-      <c r="C14" s="134"/>
-      <c r="D14" s="134"/>
+      <c r="A14" s="137"/>
+      <c r="B14" s="138"/>
+      <c r="C14" s="138"/>
+      <c r="D14" s="138"/>
       <c r="E14" s="36" t="s">
         <v>338</v>
       </c>
@@ -6648,10 +6781,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="133"/>
-      <c r="B15" s="134"/>
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
+      <c r="A15" s="137"/>
+      <c r="B15" s="138"/>
+      <c r="C15" s="138"/>
+      <c r="D15" s="138"/>
       <c r="E15" s="36" t="s">
         <v>339</v>
       </c>
@@ -6660,10 +6793,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="133"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
+      <c r="A16" s="137"/>
+      <c r="B16" s="138"/>
+      <c r="C16" s="138"/>
+      <c r="D16" s="138"/>
       <c r="E16" s="36" t="s">
         <v>340</v>
       </c>
@@ -6672,10 +6805,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" s="133"/>
-      <c r="B17" s="134"/>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
+      <c r="A17" s="137"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
+      <c r="D17" s="138"/>
       <c r="E17" s="36" t="s">
         <v>341</v>
       </c>
@@ -6684,10 +6817,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" s="133"/>
-      <c r="B18" s="134"/>
-      <c r="C18" s="134"/>
-      <c r="D18" s="134"/>
+      <c r="A18" s="137"/>
+      <c r="B18" s="138"/>
+      <c r="C18" s="138"/>
+      <c r="D18" s="138"/>
       <c r="E18" s="36" t="s">
         <v>342</v>
       </c>
@@ -6696,10 +6829,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" s="133"/>
-      <c r="B19" s="134"/>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
+      <c r="A19" s="137"/>
+      <c r="B19" s="138"/>
+      <c r="C19" s="138"/>
+      <c r="D19" s="138"/>
       <c r="E19" s="36" t="s">
         <v>343</v>
       </c>
@@ -6708,10 +6841,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" s="133"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="134"/>
-      <c r="D20" s="134"/>
+      <c r="A20" s="137"/>
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
       <c r="E20" s="36" t="s">
         <v>344</v>
       </c>
@@ -6720,10 +6853,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" s="133"/>
-      <c r="B21" s="134"/>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
+      <c r="A21" s="137"/>
+      <c r="B21" s="138"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
       <c r="E21" s="36" t="s">
         <v>345</v>
       </c>
@@ -6732,10 +6865,10 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" s="133"/>
-      <c r="B22" s="134"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
+      <c r="A22" s="137"/>
+      <c r="B22" s="138"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
       <c r="E22" s="36" t="s">
         <v>346</v>
       </c>
@@ -6744,10 +6877,10 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" s="133"/>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
+      <c r="A23" s="137"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
       <c r="E23" s="36" t="s">
         <v>347</v>
       </c>
@@ -6756,10 +6889,10 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" s="133"/>
-      <c r="B24" s="134"/>
-      <c r="C24" s="134"/>
-      <c r="D24" s="134"/>
+      <c r="A24" s="137"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
       <c r="E24" s="36" t="s">
         <v>348</v>
       </c>
@@ -6768,10 +6901,10 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A25" s="133"/>
-      <c r="B25" s="134"/>
-      <c r="C25" s="134"/>
-      <c r="D25" s="134"/>
+      <c r="A25" s="137"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
       <c r="E25" s="36" t="s">
         <v>349</v>
       </c>
@@ -6780,10 +6913,10 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A26" s="133"/>
-      <c r="B26" s="134"/>
-      <c r="C26" s="134"/>
-      <c r="D26" s="134"/>
+      <c r="A26" s="137"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
       <c r="E26" s="36" t="s">
         <v>350</v>
       </c>
@@ -6792,10 +6925,10 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A27" s="133"/>
-      <c r="B27" s="134"/>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
+      <c r="A27" s="137"/>
+      <c r="B27" s="138"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
       <c r="E27" s="36" t="s">
         <v>351</v>
       </c>
@@ -6804,10 +6937,10 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A28" s="133"/>
-      <c r="B28" s="134"/>
-      <c r="C28" s="134"/>
-      <c r="D28" s="134"/>
+      <c r="A28" s="137"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
       <c r="E28" s="36" t="s">
         <v>352</v>
       </c>
@@ -6816,10 +6949,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A29" s="133"/>
-      <c r="B29" s="134"/>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
+      <c r="A29" s="137"/>
+      <c r="B29" s="138"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
       <c r="E29" s="36" t="s">
         <v>353</v>
       </c>
@@ -6828,10 +6961,10 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A30" s="133"/>
-      <c r="B30" s="134"/>
-      <c r="C30" s="134"/>
-      <c r="D30" s="134"/>
+      <c r="A30" s="137"/>
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
       <c r="E30" s="36" t="s">
         <v>354</v>
       </c>
@@ -6840,10 +6973,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A31" s="133"/>
-      <c r="B31" s="134"/>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
+      <c r="A31" s="137"/>
+      <c r="B31" s="138"/>
+      <c r="C31" s="138"/>
+      <c r="D31" s="138"/>
       <c r="E31" s="36" t="s">
         <v>355</v>
       </c>
@@ -6852,10 +6985,10 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A32" s="133"/>
-      <c r="B32" s="134"/>
-      <c r="C32" s="134"/>
-      <c r="D32" s="134"/>
+      <c r="A32" s="137"/>
+      <c r="B32" s="138"/>
+      <c r="C32" s="138"/>
+      <c r="D32" s="138"/>
       <c r="E32" s="36" t="s">
         <v>356</v>
       </c>
@@ -6864,10 +6997,10 @@
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A33" s="133"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
+      <c r="A33" s="137"/>
+      <c r="B33" s="138"/>
+      <c r="C33" s="138"/>
+      <c r="D33" s="138"/>
       <c r="E33" s="36" t="s">
         <v>357</v>
       </c>
@@ -6876,20 +7009,20 @@
       </c>
     </row>
     <row r="34" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="133"/>
-      <c r="B34" s="134"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="134"/>
+      <c r="A34" s="137"/>
+      <c r="B34" s="138"/>
+      <c r="C34" s="138"/>
+      <c r="D34" s="138"/>
       <c r="E34" s="36"/>
       <c r="F34" s="38"/>
       <c r="G34" s="8"/>
       <c r="H34" s="39"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A35" s="133"/>
-      <c r="B35" s="134"/>
-      <c r="C35" s="134"/>
-      <c r="D35" s="134"/>
+      <c r="A35" s="137"/>
+      <c r="B35" s="138"/>
+      <c r="C35" s="138"/>
+      <c r="D35" s="138"/>
       <c r="E35" s="36" t="s">
         <v>358</v>
       </c>
@@ -6898,18 +7031,18 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="133"/>
-      <c r="B36" s="134"/>
-      <c r="C36" s="134"/>
-      <c r="D36" s="134"/>
+      <c r="A36" s="137"/>
+      <c r="B36" s="138"/>
+      <c r="C36" s="138"/>
+      <c r="D36" s="138"/>
       <c r="E36" s="36"/>
       <c r="F36" s="38"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A37" s="133"/>
-      <c r="B37" s="134"/>
-      <c r="C37" s="134"/>
-      <c r="D37" s="134"/>
+      <c r="A37" s="137"/>
+      <c r="B37" s="138"/>
+      <c r="C37" s="138"/>
+      <c r="D37" s="138"/>
       <c r="E37" s="36" t="s">
         <v>359</v>
       </c>
@@ -6918,10 +7051,10 @@
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A38" s="133"/>
-      <c r="B38" s="134"/>
-      <c r="C38" s="134"/>
-      <c r="D38" s="134"/>
+      <c r="A38" s="137"/>
+      <c r="B38" s="138"/>
+      <c r="C38" s="138"/>
+      <c r="D38" s="138"/>
       <c r="E38" s="36" t="s">
         <v>360</v>
       </c>
@@ -6930,10 +7063,10 @@
       </c>
     </row>
     <row r="39" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="127"/>
-      <c r="B39" s="131"/>
-      <c r="C39" s="131"/>
-      <c r="D39" s="131"/>
+      <c r="A39" s="131"/>
+      <c r="B39" s="135"/>
+      <c r="C39" s="135"/>
+      <c r="D39" s="135"/>
       <c r="E39" s="40" t="s">
         <v>361</v>
       </c>
@@ -6942,16 +7075,16 @@
       </c>
     </row>
     <row r="40" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A40" s="132" t="s">
+      <c r="A40" s="136" t="s">
         <v>362</v>
       </c>
-      <c r="B40" s="130" t="s">
+      <c r="B40" s="134" t="s">
         <v>363</v>
       </c>
-      <c r="C40" s="130">
-        <v>0</v>
-      </c>
-      <c r="D40" s="130" t="s">
+      <c r="C40" s="134">
+        <v>0</v>
+      </c>
+      <c r="D40" s="134" t="s">
         <v>364</v>
       </c>
       <c r="E40" s="42" t="s">
@@ -6962,18 +7095,18 @@
       </c>
     </row>
     <row r="41" spans="1:8" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="133"/>
-      <c r="B41" s="134"/>
-      <c r="C41" s="134"/>
-      <c r="D41" s="134"/>
+      <c r="A41" s="137"/>
+      <c r="B41" s="138"/>
+      <c r="C41" s="138"/>
+      <c r="D41" s="138"/>
       <c r="E41" s="44"/>
       <c r="F41" s="45"/>
     </row>
     <row r="42" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A42" s="133"/>
-      <c r="B42" s="134"/>
-      <c r="C42" s="134"/>
-      <c r="D42" s="134"/>
+      <c r="A42" s="137"/>
+      <c r="B42" s="138"/>
+      <c r="C42" s="138"/>
+      <c r="D42" s="138"/>
       <c r="E42" s="44" t="s">
         <v>366</v>
       </c>
@@ -6982,10 +7115,10 @@
       </c>
     </row>
     <row r="43" spans="1:8" ht="17" x14ac:dyDescent="0.2">
-      <c r="A43" s="133"/>
-      <c r="B43" s="134"/>
-      <c r="C43" s="134"/>
-      <c r="D43" s="134"/>
+      <c r="A43" s="137"/>
+      <c r="B43" s="138"/>
+      <c r="C43" s="138"/>
+      <c r="D43" s="138"/>
       <c r="E43" s="44" t="s">
         <v>367</v>
       </c>
@@ -6995,9 +7128,9 @@
     </row>
     <row r="44" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="30"/>
-      <c r="B44" s="134"/>
-      <c r="C44" s="134"/>
-      <c r="D44" s="134"/>
+      <c r="B44" s="138"/>
+      <c r="C44" s="138"/>
+      <c r="D44" s="138"/>
       <c r="E44" s="44" t="s">
         <v>368</v>
       </c>
@@ -7007,9 +7140,9 @@
     </row>
     <row r="45" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="30"/>
-      <c r="B45" s="134"/>
-      <c r="C45" s="134"/>
-      <c r="D45" s="134"/>
+      <c r="B45" s="138"/>
+      <c r="C45" s="138"/>
+      <c r="D45" s="138"/>
       <c r="E45" s="44" t="s">
         <v>369</v>
       </c>
@@ -7019,9 +7152,9 @@
     </row>
     <row r="46" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="30"/>
-      <c r="B46" s="134"/>
-      <c r="C46" s="134"/>
-      <c r="D46" s="134"/>
+      <c r="B46" s="138"/>
+      <c r="C46" s="138"/>
+      <c r="D46" s="138"/>
       <c r="E46" s="44" t="s">
         <v>370</v>
       </c>
@@ -7031,9 +7164,9 @@
     </row>
     <row r="47" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A47" s="30"/>
-      <c r="B47" s="134"/>
-      <c r="C47" s="134"/>
-      <c r="D47" s="134"/>
+      <c r="B47" s="138"/>
+      <c r="C47" s="138"/>
+      <c r="D47" s="138"/>
       <c r="E47" s="44" t="s">
         <v>371</v>
       </c>
@@ -7043,9 +7176,9 @@
     </row>
     <row r="48" spans="1:8" ht="17" x14ac:dyDescent="0.2">
       <c r="A48" s="30"/>
-      <c r="B48" s="134"/>
-      <c r="C48" s="134"/>
-      <c r="D48" s="134"/>
+      <c r="B48" s="138"/>
+      <c r="C48" s="138"/>
+      <c r="D48" s="138"/>
       <c r="E48" s="44" t="s">
         <v>372</v>
       </c>
@@ -7055,17 +7188,17 @@
     </row>
     <row r="49" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="30"/>
-      <c r="B49" s="134"/>
-      <c r="C49" s="134"/>
-      <c r="D49" s="134"/>
+      <c r="B49" s="138"/>
+      <c r="C49" s="138"/>
+      <c r="D49" s="138"/>
       <c r="E49" s="44"/>
       <c r="F49" s="45"/>
     </row>
     <row r="50" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="30"/>
-      <c r="B50" s="134"/>
-      <c r="C50" s="134"/>
-      <c r="D50" s="134"/>
+      <c r="B50" s="138"/>
+      <c r="C50" s="138"/>
+      <c r="D50" s="138"/>
       <c r="E50" s="44" t="s">
         <v>373</v>
       </c>
@@ -7075,9 +7208,9 @@
     </row>
     <row r="51" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="30"/>
-      <c r="B51" s="134"/>
-      <c r="C51" s="134"/>
-      <c r="D51" s="134"/>
+      <c r="B51" s="138"/>
+      <c r="C51" s="138"/>
+      <c r="D51" s="138"/>
       <c r="E51" s="44" t="s">
         <v>374</v>
       </c>
@@ -7087,9 +7220,9 @@
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="30"/>
-      <c r="B52" s="134"/>
-      <c r="C52" s="134"/>
-      <c r="D52" s="134"/>
+      <c r="B52" s="138"/>
+      <c r="C52" s="138"/>
+      <c r="D52" s="138"/>
       <c r="E52" s="44" t="s">
         <v>375</v>
       </c>
@@ -7099,9 +7232,9 @@
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="30"/>
-      <c r="B53" s="134"/>
-      <c r="C53" s="134"/>
-      <c r="D53" s="134"/>
+      <c r="B53" s="138"/>
+      <c r="C53" s="138"/>
+      <c r="D53" s="138"/>
       <c r="E53" s="44" t="s">
         <v>376</v>
       </c>
@@ -7111,9 +7244,9 @@
     </row>
     <row r="54" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="30"/>
-      <c r="B54" s="134"/>
-      <c r="C54" s="134"/>
-      <c r="D54" s="134"/>
+      <c r="B54" s="138"/>
+      <c r="C54" s="138"/>
+      <c r="D54" s="138"/>
       <c r="E54" s="44" t="s">
         <v>377</v>
       </c>
@@ -7123,17 +7256,17 @@
     </row>
     <row r="55" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="30"/>
-      <c r="B55" s="134"/>
-      <c r="C55" s="134"/>
-      <c r="D55" s="134"/>
+      <c r="B55" s="138"/>
+      <c r="C55" s="138"/>
+      <c r="D55" s="138"/>
       <c r="E55" s="44"/>
       <c r="F55" s="37"/>
     </row>
     <row r="56" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="30"/>
-      <c r="B56" s="134"/>
-      <c r="C56" s="134"/>
-      <c r="D56" s="134"/>
+      <c r="B56" s="138"/>
+      <c r="C56" s="138"/>
+      <c r="D56" s="138"/>
       <c r="E56" s="44" t="s">
         <v>378</v>
       </c>
@@ -7143,25 +7276,25 @@
     </row>
     <row r="57" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="30"/>
-      <c r="B57" s="134"/>
-      <c r="C57" s="134"/>
-      <c r="D57" s="134"/>
+      <c r="B57" s="138"/>
+      <c r="C57" s="138"/>
+      <c r="D57" s="138"/>
       <c r="E57" s="44"/>
       <c r="F57" s="45"/>
     </row>
     <row r="58" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="30"/>
-      <c r="B58" s="134"/>
-      <c r="C58" s="134"/>
-      <c r="D58" s="134"/>
+      <c r="B58" s="138"/>
+      <c r="C58" s="138"/>
+      <c r="D58" s="138"/>
       <c r="E58" s="44"/>
       <c r="F58" s="45"/>
     </row>
     <row r="59" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="30"/>
-      <c r="B59" s="134"/>
-      <c r="C59" s="134"/>
-      <c r="D59" s="134"/>
+      <c r="B59" s="138"/>
+      <c r="C59" s="138"/>
+      <c r="D59" s="138"/>
       <c r="E59" s="44" t="s">
         <v>379</v>
       </c>
@@ -7171,9 +7304,9 @@
     </row>
     <row r="60" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="30"/>
-      <c r="B60" s="134"/>
-      <c r="C60" s="134"/>
-      <c r="D60" s="134"/>
+      <c r="B60" s="138"/>
+      <c r="C60" s="138"/>
+      <c r="D60" s="138"/>
       <c r="E60" s="44" t="s">
         <v>380</v>
       </c>
@@ -7183,9 +7316,9 @@
     </row>
     <row r="61" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="30"/>
-      <c r="B61" s="134"/>
-      <c r="C61" s="134"/>
-      <c r="D61" s="134"/>
+      <c r="B61" s="138"/>
+      <c r="C61" s="138"/>
+      <c r="D61" s="138"/>
       <c r="E61" s="44" t="s">
         <v>381</v>
       </c>
@@ -7195,25 +7328,25 @@
     </row>
     <row r="62" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="30"/>
-      <c r="B62" s="134"/>
-      <c r="C62" s="134"/>
-      <c r="D62" s="134"/>
+      <c r="B62" s="138"/>
+      <c r="C62" s="138"/>
+      <c r="D62" s="138"/>
       <c r="E62" s="44"/>
       <c r="F62" s="45"/>
     </row>
     <row r="63" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="30"/>
-      <c r="B63" s="134"/>
-      <c r="C63" s="134"/>
-      <c r="D63" s="134"/>
+      <c r="B63" s="138"/>
+      <c r="C63" s="138"/>
+      <c r="D63" s="138"/>
       <c r="E63" s="44"/>
       <c r="F63" s="45"/>
     </row>
     <row r="64" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A64" s="30"/>
-      <c r="B64" s="131"/>
-      <c r="C64" s="131"/>
-      <c r="D64" s="131"/>
+      <c r="B64" s="135"/>
+      <c r="C64" s="135"/>
+      <c r="D64" s="135"/>
       <c r="E64" s="46"/>
       <c r="F64" s="47"/>
     </row>
@@ -7230,22 +7363,22 @@
       <c r="D65" s="91" t="s">
         <v>385</v>
       </c>
-      <c r="E65" s="135" t="s">
+      <c r="E65" s="139" t="s">
         <v>386</v>
       </c>
-      <c r="F65" s="136"/>
+      <c r="F65" s="140"/>
     </row>
     <row r="66" spans="1:6" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="113" t="s">
+      <c r="A66" s="117" t="s">
         <v>387</v>
       </c>
-      <c r="B66" s="115" t="s">
+      <c r="B66" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="C66" s="139" t="s">
+      <c r="C66" s="143" t="s">
         <v>389</v>
       </c>
-      <c r="D66" s="117" t="s">
+      <c r="D66" s="121" t="s">
         <v>390</v>
       </c>
       <c r="E66" s="49" t="s">
@@ -7256,18 +7389,18 @@
       </c>
     </row>
     <row r="67" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="114"/>
-      <c r="B67" s="116"/>
-      <c r="C67" s="140"/>
-      <c r="D67" s="118"/>
+      <c r="A67" s="118"/>
+      <c r="B67" s="120"/>
+      <c r="C67" s="144"/>
+      <c r="D67" s="122"/>
       <c r="E67" s="51"/>
       <c r="F67" s="52"/>
     </row>
     <row r="68" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="114"/>
-      <c r="B68" s="116"/>
-      <c r="C68" s="140"/>
-      <c r="D68" s="118"/>
+      <c r="A68" s="118"/>
+      <c r="B68" s="120"/>
+      <c r="C68" s="144"/>
+      <c r="D68" s="122"/>
       <c r="E68" s="51" t="s">
         <v>392</v>
       </c>
@@ -7276,18 +7409,18 @@
       </c>
     </row>
     <row r="69" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="114"/>
-      <c r="B69" s="116"/>
-      <c r="C69" s="140"/>
-      <c r="D69" s="118"/>
+      <c r="A69" s="118"/>
+      <c r="B69" s="120"/>
+      <c r="C69" s="144"/>
+      <c r="D69" s="122"/>
       <c r="E69" s="51"/>
       <c r="F69" s="52"/>
     </row>
     <row r="70" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="114"/>
-      <c r="B70" s="116"/>
-      <c r="C70" s="140"/>
-      <c r="D70" s="118"/>
+      <c r="A70" s="118"/>
+      <c r="B70" s="120"/>
+      <c r="C70" s="144"/>
+      <c r="D70" s="122"/>
       <c r="E70" s="51" t="s">
         <v>393</v>
       </c>
@@ -7296,10 +7429,10 @@
       </c>
     </row>
     <row r="71" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="114"/>
-      <c r="B71" s="116"/>
-      <c r="C71" s="140"/>
-      <c r="D71" s="118"/>
+      <c r="A71" s="118"/>
+      <c r="B71" s="120"/>
+      <c r="C71" s="144"/>
+      <c r="D71" s="122"/>
       <c r="E71" s="51" t="s">
         <v>394</v>
       </c>
@@ -7308,18 +7441,18 @@
       </c>
     </row>
     <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="114"/>
-      <c r="B72" s="116"/>
-      <c r="C72" s="140"/>
-      <c r="D72" s="118"/>
+      <c r="A72" s="118"/>
+      <c r="B72" s="120"/>
+      <c r="C72" s="144"/>
+      <c r="D72" s="122"/>
       <c r="E72" s="51"/>
       <c r="F72" s="52"/>
     </row>
     <row r="73" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="114"/>
-      <c r="B73" s="116"/>
-      <c r="C73" s="140"/>
-      <c r="D73" s="118"/>
+      <c r="A73" s="118"/>
+      <c r="B73" s="120"/>
+      <c r="C73" s="144"/>
+      <c r="D73" s="122"/>
       <c r="E73" s="51" t="s">
         <v>395</v>
       </c>
@@ -7328,18 +7461,18 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="114"/>
-      <c r="B74" s="116"/>
-      <c r="C74" s="140"/>
-      <c r="D74" s="118"/>
+      <c r="A74" s="118"/>
+      <c r="B74" s="120"/>
+      <c r="C74" s="144"/>
+      <c r="D74" s="122"/>
       <c r="E74" s="51"/>
       <c r="F74" s="52"/>
     </row>
     <row r="75" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="137"/>
-      <c r="B75" s="138"/>
-      <c r="C75" s="141"/>
-      <c r="D75" s="142"/>
+      <c r="A75" s="141"/>
+      <c r="B75" s="142"/>
+      <c r="C75" s="145"/>
+      <c r="D75" s="146"/>
       <c r="E75" s="53" t="s">
         <v>396</v>
       </c>
@@ -7348,26 +7481,26 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="29.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="113" t="s">
+      <c r="A76" s="117" t="s">
         <v>397</v>
       </c>
-      <c r="B76" s="115" t="s">
+      <c r="B76" s="119" t="s">
         <v>398</v>
       </c>
-      <c r="C76" s="146" t="s">
+      <c r="C76" s="150" t="s">
         <v>389</v>
       </c>
-      <c r="D76" s="143" t="s">
+      <c r="D76" s="147" t="s">
         <v>399</v>
       </c>
       <c r="E76" s="81"/>
       <c r="F76" s="82"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A77" s="114"/>
-      <c r="B77" s="116"/>
-      <c r="C77" s="147"/>
-      <c r="D77" s="144"/>
+      <c r="A77" s="118"/>
+      <c r="B77" s="120"/>
+      <c r="C77" s="151"/>
+      <c r="D77" s="148"/>
       <c r="E77" s="83" t="s">
         <v>400</v>
       </c>
@@ -7376,10 +7509,10 @@
       </c>
     </row>
     <row r="78" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="137"/>
-      <c r="B78" s="138"/>
-      <c r="C78" s="148"/>
-      <c r="D78" s="145"/>
+      <c r="A78" s="141"/>
+      <c r="B78" s="142"/>
+      <c r="C78" s="152"/>
+      <c r="D78" s="149"/>
       <c r="E78" s="85" t="s">
         <v>401</v>
       </c>
@@ -7388,16 +7521,16 @@
       </c>
     </row>
     <row r="79" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="113" t="s">
+      <c r="A79" s="117" t="s">
         <v>402</v>
       </c>
-      <c r="B79" s="115" t="s">
+      <c r="B79" s="119" t="s">
         <v>403</v>
       </c>
-      <c r="C79" s="115" t="s">
+      <c r="C79" s="119" t="s">
         <v>404</v>
       </c>
-      <c r="D79" s="143" t="s">
+      <c r="D79" s="147" t="s">
         <v>405</v>
       </c>
       <c r="E79" s="87" t="s">
@@ -7408,32 +7541,32 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A80" s="114"/>
-      <c r="B80" s="116"/>
-      <c r="C80" s="116"/>
-      <c r="D80" s="144"/>
+      <c r="A80" s="118"/>
+      <c r="B80" s="120"/>
+      <c r="C80" s="120"/>
+      <c r="D80" s="148"/>
       <c r="E80" s="83"/>
       <c r="F80" s="89"/>
     </row>
     <row r="81" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="137"/>
-      <c r="B81" s="138"/>
-      <c r="C81" s="138"/>
-      <c r="D81" s="145"/>
+      <c r="A81" s="141"/>
+      <c r="B81" s="142"/>
+      <c r="C81" s="142"/>
+      <c r="D81" s="149"/>
       <c r="E81" s="85"/>
       <c r="F81" s="90"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A82" s="149" t="s">
+      <c r="A82" s="153" t="s">
         <v>407</v>
       </c>
-      <c r="B82" s="151" t="s">
+      <c r="B82" s="155" t="s">
         <v>408</v>
       </c>
-      <c r="C82" s="153">
-        <v>0</v>
-      </c>
-      <c r="D82" s="153" t="s">
+      <c r="C82" s="157">
+        <v>0</v>
+      </c>
+      <c r="D82" s="157" t="s">
         <v>409</v>
       </c>
       <c r="E82" s="96" t="s">
@@ -7444,19 +7577,19 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A83" s="150"/>
-      <c r="B83" s="152"/>
-      <c r="C83" s="154"/>
-      <c r="D83" s="154"/>
+      <c r="A83" s="154"/>
+      <c r="B83" s="156"/>
+      <c r="C83" s="158"/>
+      <c r="D83" s="158"/>
       <c r="E83" s="98"/>
       <c r="F83" s="99"/>
       <c r="G83" s="55"/>
     </row>
     <row r="84" spans="1:7" s="56" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="150"/>
-      <c r="B84" s="152"/>
-      <c r="C84" s="154"/>
-      <c r="D84" s="154"/>
+      <c r="A84" s="154"/>
+      <c r="B84" s="156"/>
+      <c r="C84" s="158"/>
+      <c r="D84" s="158"/>
       <c r="E84" s="98" t="s">
         <v>411</v>
       </c>
@@ -7465,10 +7598,10 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A85" s="150"/>
-      <c r="B85" s="152"/>
-      <c r="C85" s="154"/>
-      <c r="D85" s="154"/>
+      <c r="A85" s="154"/>
+      <c r="B85" s="156"/>
+      <c r="C85" s="158"/>
+      <c r="D85" s="158"/>
       <c r="E85" s="98" t="s">
         <v>412</v>
       </c>
@@ -7477,10 +7610,10 @@
       </c>
     </row>
     <row r="86" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="150"/>
-      <c r="B86" s="152"/>
-      <c r="C86" s="154"/>
-      <c r="D86" s="155"/>
+      <c r="A86" s="154"/>
+      <c r="B86" s="156"/>
+      <c r="C86" s="158"/>
+      <c r="D86" s="159"/>
       <c r="E86" s="100" t="s">
         <v>413</v>
       </c>
@@ -7489,16 +7622,16 @@
       </c>
     </row>
     <row r="87" spans="1:7" ht="43.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="132" t="s">
+      <c r="A87" s="136" t="s">
         <v>414</v>
       </c>
-      <c r="B87" s="132" t="s">
+      <c r="B87" s="136" t="s">
         <v>415</v>
       </c>
-      <c r="C87" s="130">
-        <v>0</v>
-      </c>
-      <c r="D87" s="130" t="s">
+      <c r="C87" s="134">
+        <v>0</v>
+      </c>
+      <c r="D87" s="134" t="s">
         <v>416</v>
       </c>
       <c r="E87" s="57" t="s">
@@ -7509,10 +7642,10 @@
       </c>
     </row>
     <row r="88" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="133"/>
-      <c r="B88" s="133"/>
-      <c r="C88" s="134"/>
-      <c r="D88" s="134"/>
+      <c r="A88" s="137"/>
+      <c r="B88" s="137"/>
+      <c r="C88" s="138"/>
+      <c r="D88" s="138"/>
       <c r="E88" s="59" t="s">
         <v>418</v>
       </c>
@@ -7521,18 +7654,18 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="133"/>
-      <c r="B89" s="133"/>
-      <c r="C89" s="134"/>
-      <c r="D89" s="134"/>
+      <c r="A89" s="137"/>
+      <c r="B89" s="137"/>
+      <c r="C89" s="138"/>
+      <c r="D89" s="138"/>
       <c r="E89" s="59"/>
       <c r="F89" s="60"/>
     </row>
     <row r="90" spans="1:7" ht="16" x14ac:dyDescent="0.2">
-      <c r="A90" s="133"/>
-      <c r="B90" s="133"/>
-      <c r="C90" s="134"/>
-      <c r="D90" s="134"/>
+      <c r="A90" s="137"/>
+      <c r="B90" s="137"/>
+      <c r="C90" s="138"/>
+      <c r="D90" s="138"/>
       <c r="E90" s="61" t="s">
         <v>419</v>
       </c>
@@ -7541,10 +7674,10 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="133"/>
-      <c r="B91" s="133"/>
-      <c r="C91" s="134"/>
-      <c r="D91" s="134"/>
+      <c r="A91" s="137"/>
+      <c r="B91" s="137"/>
+      <c r="C91" s="138"/>
+      <c r="D91" s="138"/>
       <c r="E91" s="61"/>
       <c r="F91" s="62"/>
     </row>
@@ -7567,42 +7700,42 @@
       <c r="F92" s="71"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A93" s="113" t="s">
+      <c r="A93" s="117" t="s">
         <v>430</v>
       </c>
-      <c r="B93" s="115" t="s">
+      <c r="B93" s="119" t="s">
         <v>431</v>
       </c>
-      <c r="C93" s="115" t="s">
+      <c r="C93" s="119" t="s">
         <v>432</v>
       </c>
-      <c r="D93" s="115" t="s">
+      <c r="D93" s="119" t="s">
         <v>433</v>
       </c>
-      <c r="E93" s="168" t="s">
+      <c r="E93" s="172" t="s">
         <v>434</v>
       </c>
-      <c r="F93" s="169"/>
+      <c r="F93" s="173"/>
     </row>
     <row r="94" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="137"/>
-      <c r="B94" s="138"/>
-      <c r="C94" s="138"/>
-      <c r="D94" s="138"/>
-      <c r="E94" s="170"/>
-      <c r="F94" s="171"/>
+      <c r="A94" s="141"/>
+      <c r="B94" s="142"/>
+      <c r="C94" s="142"/>
+      <c r="D94" s="142"/>
+      <c r="E94" s="174"/>
+      <c r="F94" s="175"/>
     </row>
     <row r="95" spans="1:7" ht="29.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="113" t="s">
+      <c r="A95" s="117" t="s">
         <v>435</v>
       </c>
-      <c r="B95" s="115" t="s">
+      <c r="B95" s="119" t="s">
         <v>436</v>
       </c>
-      <c r="C95" s="115" t="s">
+      <c r="C95" s="119" t="s">
         <v>437</v>
       </c>
-      <c r="D95" s="115" t="s">
+      <c r="D95" s="119" t="s">
         <v>438</v>
       </c>
       <c r="E95" s="72" t="s">
@@ -7611,10 +7744,10 @@
       <c r="F95" s="73"/>
     </row>
     <row r="96" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="137"/>
-      <c r="B96" s="138"/>
-      <c r="C96" s="138"/>
-      <c r="D96" s="138"/>
+      <c r="A96" s="141"/>
+      <c r="B96" s="142"/>
+      <c r="C96" s="142"/>
+      <c r="D96" s="142"/>
       <c r="E96" s="74" t="s">
         <v>440</v>
       </c>
@@ -7641,16 +7774,16 @@
       </c>
     </row>
     <row r="98" spans="1:6" ht="43.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="149" t="s">
+      <c r="A98" s="153" t="s">
         <v>420</v>
       </c>
-      <c r="B98" s="163" t="s">
+      <c r="B98" s="167" t="s">
         <v>325</v>
       </c>
-      <c r="C98" s="151">
-        <v>0</v>
-      </c>
-      <c r="D98" s="166">
+      <c r="C98" s="155">
+        <v>0</v>
+      </c>
+      <c r="D98" s="170">
         <v>100</v>
       </c>
       <c r="E98" s="57" t="s">
@@ -7661,34 +7794,34 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="162"/>
-      <c r="B99" s="164"/>
-      <c r="C99" s="165"/>
-      <c r="D99" s="167"/>
+      <c r="A99" s="166"/>
+      <c r="B99" s="168"/>
+      <c r="C99" s="169"/>
+      <c r="D99" s="171"/>
       <c r="E99" s="65"/>
       <c r="F99" s="66"/>
     </row>
     <row r="100" spans="1:6" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="156" t="s">
+      <c r="A100" s="160" t="s">
         <v>422</v>
       </c>
-      <c r="B100" s="156" t="s">
+      <c r="B100" s="160" t="s">
         <v>423</v>
       </c>
-      <c r="C100" s="158">
-        <v>0</v>
-      </c>
-      <c r="D100" s="160">
+      <c r="C100" s="162">
+        <v>0</v>
+      </c>
+      <c r="D100" s="164">
         <v>50</v>
       </c>
       <c r="E100" s="57"/>
       <c r="F100" s="58"/>
     </row>
     <row r="101" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="157"/>
-      <c r="B101" s="157"/>
-      <c r="C101" s="159"/>
-      <c r="D101" s="161"/>
+      <c r="A101" s="161"/>
+      <c r="B101" s="161"/>
+      <c r="C101" s="163"/>
+      <c r="D101" s="165"/>
       <c r="E101" s="67" t="s">
         <v>424</v>
       </c>
@@ -7770,6 +7903,221 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE88F733-6F29-D94D-A850-4ADD3FEB4AB6}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="2" width="41.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="58" style="5" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="20" x14ac:dyDescent="0.2">
+      <c r="A1" s="176" t="s">
+        <v>521</v>
+      </c>
+      <c r="B1" s="176"/>
+      <c r="C1" s="176"/>
+    </row>
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A2" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="106" t="s">
+        <v>495</v>
+      </c>
+      <c r="C2" s="106" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A3" s="179" t="s">
+        <v>494</v>
+      </c>
+      <c r="B3" s="179"/>
+      <c r="C3" s="179"/>
+    </row>
+    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A4" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="108" t="s">
+        <v>496</v>
+      </c>
+      <c r="C4" s="177" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A5" s="108" t="s">
+        <v>497</v>
+      </c>
+      <c r="B5" s="108" t="s">
+        <v>497</v>
+      </c>
+      <c r="C5" s="178"/>
+    </row>
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A6" s="108" t="s">
+        <v>498</v>
+      </c>
+      <c r="B6" s="108" t="s">
+        <v>498</v>
+      </c>
+      <c r="C6" s="178"/>
+    </row>
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A7" s="108" t="s">
+        <v>499</v>
+      </c>
+      <c r="B7" s="108" t="s">
+        <v>499</v>
+      </c>
+      <c r="C7" s="178"/>
+    </row>
+    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="108" t="s">
+        <v>500</v>
+      </c>
+      <c r="B8" s="108" t="s">
+        <v>500</v>
+      </c>
+      <c r="C8" s="178"/>
+    </row>
+    <row r="9" spans="1:3" ht="38" x14ac:dyDescent="0.2">
+      <c r="A9" s="108" t="s">
+        <v>501</v>
+      </c>
+      <c r="B9" s="109" t="s">
+        <v>504</v>
+      </c>
+      <c r="C9" s="178"/>
+    </row>
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A10" s="108" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10" s="108" t="s">
+        <v>505</v>
+      </c>
+      <c r="C10" s="178"/>
+    </row>
+    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A11" s="108" t="s">
+        <v>502</v>
+      </c>
+      <c r="B11" s="108" t="s">
+        <v>502</v>
+      </c>
+      <c r="C11" s="178"/>
+    </row>
+    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A12" s="108" t="s">
+        <v>503</v>
+      </c>
+      <c r="B12" s="108" t="s">
+        <v>506</v>
+      </c>
+      <c r="C12" s="178"/>
+    </row>
+    <row r="13" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A13" s="108" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="109" t="s">
+        <v>507</v>
+      </c>
+      <c r="C13" s="178"/>
+    </row>
+    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A14" s="179" t="s">
+        <v>508</v>
+      </c>
+      <c r="B14" s="179"/>
+      <c r="C14" s="179"/>
+    </row>
+    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A15" s="108" t="s">
+        <v>509</v>
+      </c>
+      <c r="B15" s="108" t="s">
+        <v>505</v>
+      </c>
+      <c r="C15" s="107" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="57" x14ac:dyDescent="0.2">
+      <c r="A16" s="108" t="s">
+        <v>510</v>
+      </c>
+      <c r="B16" s="109" t="s">
+        <v>512</v>
+      </c>
+      <c r="C16" s="177" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="38" x14ac:dyDescent="0.2">
+      <c r="A17" s="108" t="s">
+        <v>511</v>
+      </c>
+      <c r="B17" s="109" t="s">
+        <v>513</v>
+      </c>
+      <c r="C17" s="178"/>
+    </row>
+    <row r="18" spans="1:3" ht="38" x14ac:dyDescent="0.2">
+      <c r="A18" s="108" t="s">
+        <v>514</v>
+      </c>
+      <c r="B18" s="109" t="s">
+        <v>515</v>
+      </c>
+      <c r="C18" s="178"/>
+    </row>
+    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A19" s="107"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="107"/>
+    </row>
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A20" s="107" t="s">
+        <v>519</v>
+      </c>
+      <c r="B20" s="107"/>
+      <c r="C20" s="107"/>
+    </row>
+    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A21" s="107" t="s">
+        <v>520</v>
+      </c>
+      <c r="B21" s="107"/>
+      <c r="C21" s="107"/>
+    </row>
+    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A22" s="107"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="107"/>
+    </row>
+    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.2">
+      <c r="A23" s="107"/>
+      <c r="B23" s="107"/>
+      <c r="C23" s="107"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="C4:C13"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="C16:C18"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet6"/>
@@ -7821,7 +8169,7 @@
       <c r="E2" s="13"/>
       <c r="F2" s="13"/>
       <c r="G2" s="13"/>
-      <c r="H2" s="106" t="s">
+      <c r="H2" s="110" t="s">
         <v>255</v>
       </c>
     </row>
@@ -7847,7 +8195,7 @@
       <c r="G3" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="106"/>
+      <c r="H3" s="110"/>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -7871,7 +8219,7 @@
       <c r="G4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="106"/>
+      <c r="H4" s="110"/>
     </row>
     <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -7895,7 +8243,7 @@
       <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="106"/>
+      <c r="H5" s="110"/>
     </row>
     <row r="6" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -7919,7 +8267,7 @@
       <c r="G6" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="106"/>
+      <c r="H6" s="110"/>
     </row>
     <row r="7" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -7943,7 +8291,7 @@
       <c r="G7" t="s">
         <v>38</v>
       </c>
-      <c r="H7" s="106"/>
+      <c r="H7" s="110"/>
     </row>
     <row r="8" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -7967,7 +8315,7 @@
       <c r="G8" t="s">
         <v>39</v>
       </c>
-      <c r="H8" s="106"/>
+      <c r="H8" s="110"/>
     </row>
     <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -7991,7 +8339,7 @@
       <c r="G9" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="106"/>
+      <c r="H9" s="110"/>
     </row>
     <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8015,7 +8363,7 @@
       <c r="G10" t="s">
         <v>33</v>
       </c>
-      <c r="H10" s="106"/>
+      <c r="H10" s="110"/>
     </row>
     <row r="11" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -8039,7 +8387,7 @@
       <c r="G11" t="s">
         <v>134</v>
       </c>
-      <c r="H11" s="106"/>
+      <c r="H11" s="110"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="11" t="s">
@@ -8051,7 +8399,7 @@
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19"/>
-      <c r="H12" s="106"/>
+      <c r="H12" s="110"/>
     </row>
     <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
@@ -8075,7 +8423,7 @@
       <c r="G13" t="s">
         <v>43</v>
       </c>
-      <c r="H13" s="106"/>
+      <c r="H13" s="110"/>
     </row>
     <row r="14" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
@@ -8099,7 +8447,7 @@
       <c r="G14" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="106"/>
+      <c r="H14" s="110"/>
     </row>
     <row r="15" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
@@ -8123,7 +8471,7 @@
       <c r="G15" t="s">
         <v>41</v>
       </c>
-      <c r="H15" s="106"/>
+      <c r="H15" s="110"/>
     </row>
     <row r="16" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
@@ -8147,7 +8495,7 @@
       <c r="G16" t="s">
         <v>42</v>
       </c>
-      <c r="H16" s="106"/>
+      <c r="H16" s="110"/>
     </row>
     <row r="17" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B17" s="9"/>
@@ -8238,7 +8586,7 @@
         <v>63</v>
       </c>
       <c r="F2" s="20"/>
-      <c r="G2" s="108" t="s">
+      <c r="G2" s="112" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8259,7 +8607,7 @@
         <v>64</v>
       </c>
       <c r="F3" s="20"/>
-      <c r="G3" s="108"/>
+      <c r="G3" s="112"/>
     </row>
     <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -8278,7 +8626,7 @@
         <v>309</v>
       </c>
       <c r="F4" s="21"/>
-      <c r="G4" s="108"/>
+      <c r="G4" s="112"/>
     </row>
     <row r="5" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8297,7 +8645,7 @@
         <v>65</v>
       </c>
       <c r="F5" s="20"/>
-      <c r="G5" s="108"/>
+      <c r="G5" s="112"/>
     </row>
     <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -8316,7 +8664,7 @@
         <v>250</v>
       </c>
       <c r="F6" s="20"/>
-      <c r="G6" s="108"/>
+      <c r="G6" s="112"/>
     </row>
     <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8335,7 +8683,7 @@
         <v>69</v>
       </c>
       <c r="F7" s="20"/>
-      <c r="G7" s="108"/>
+      <c r="G7" s="112"/>
     </row>
     <row r="8" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8354,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="20"/>
-      <c r="G8" s="108"/>
+      <c r="G8" s="112"/>
     </row>
     <row r="9" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8373,7 +8721,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="20"/>
-      <c r="G9" s="108"/>
+      <c r="G9" s="112"/>
     </row>
     <row r="10" spans="1:8" ht="224" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
@@ -8384,7 +8732,7 @@
       <c r="F10" s="8" t="s">
         <v>464</v>
       </c>
-      <c r="G10" s="108"/>
+      <c r="G10" s="112"/>
     </row>
     <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -8403,7 +8751,7 @@
         <v>71</v>
       </c>
       <c r="F11" s="20"/>
-      <c r="G11" s="108"/>
+      <c r="G11" s="112"/>
     </row>
     <row r="12" spans="1:8" ht="64" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
@@ -8422,7 +8770,7 @@
         <v>245</v>
       </c>
       <c r="F12" s="21"/>
-      <c r="G12" s="108"/>
+      <c r="G12" s="112"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -8446,8 +8794,8 @@
       </c>
       <c r="D15" s="8"/>
     </row>
-    <row r="16" spans="1:8" s="109" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="109" t="s">
+    <row r="16" spans="1:8" s="113" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="113" t="s">
         <v>493</v>
       </c>
     </row>
@@ -8509,7 +8857,7 @@
       <c r="E2" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="112" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8529,7 +8877,7 @@
       <c r="E3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -8547,7 +8895,7 @@
       <c r="E4" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8565,7 +8913,7 @@
       <c r="E5" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
@@ -8583,7 +8931,7 @@
       <c r="E6" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8598,7 +8946,7 @@
       <c r="E7" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8616,7 +8964,7 @@
       <c r="E8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8634,7 +8982,7 @@
       <c r="E9" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="112"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -8652,10 +9000,10 @@
       <c r="E10" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="112"/>
     </row>
     <row r="11" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F11" s="108"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="C12" s="9" t="s">
@@ -8736,7 +9084,7 @@
       <c r="E2" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="112" t="s">
         <v>255</v>
       </c>
     </row>
@@ -8756,7 +9104,7 @@
       <c r="E3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -8774,7 +9122,7 @@
       <c r="E4" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -8792,7 +9140,7 @@
       <c r="E5" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -8810,7 +9158,7 @@
       <c r="E6" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -8825,7 +9173,7 @@
       <c r="E7" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="57" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -8843,7 +9191,7 @@
       <c r="E8" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -8861,7 +9209,7 @@
       <c r="E9" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="112"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
@@ -8884,13 +9232,13 @@
       </c>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:6" s="110" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="110" t="s">
+    <row r="13" spans="1:6" s="114" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="114" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="109" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="109" t="s">
+    <row r="14" spans="1:6" s="113" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="113" t="s">
         <v>492</v>
       </c>
     </row>
@@ -9128,8 +9476,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="14" spans="1:6" s="111" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="111" t="s">
+    <row r="14" spans="1:6" s="115" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="115" t="s">
         <v>490</v>
       </c>
     </row>
@@ -9200,7 +9548,7 @@
       <c r="E2" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="112" t="s">
         <v>255</v>
       </c>
     </row>
@@ -9220,7 +9568,7 @@
       <c r="E3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
@@ -9238,7 +9586,7 @@
       <c r="E4" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -9256,7 +9604,7 @@
       <c r="E5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
@@ -9274,7 +9622,7 @@
       <c r="E6" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
@@ -9292,7 +9640,7 @@
       <c r="E7" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="64" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -9310,7 +9658,7 @@
       <c r="E8" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
@@ -9328,7 +9676,7 @@
       <c r="E9" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="112"/>
     </row>
     <row r="10" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
@@ -9346,7 +9694,7 @@
       <c r="E10" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="112"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
@@ -9375,8 +9723,8 @@
       </c>
       <c r="D14" s="8"/>
     </row>
-    <row r="15" spans="1:6" s="109" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="109" t="s">
+    <row r="15" spans="1:6" s="113" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="113" t="s">
         <v>492</v>
       </c>
     </row>
@@ -9443,7 +9791,7 @@
       <c r="E2" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="112" t="s">
         <v>465</v>
       </c>
     </row>
@@ -9463,7 +9811,7 @@
       <c r="E3" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -9481,7 +9829,7 @@
       <c r="E4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
@@ -9499,7 +9847,7 @@
       <c r="E5" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -9517,7 +9865,7 @@
       <c r="E6" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
@@ -9535,7 +9883,7 @@
       <c r="E7" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -9553,7 +9901,7 @@
       <c r="E8" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
@@ -9571,7 +9919,7 @@
       <c r="E9" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="112"/>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
@@ -9589,7 +9937,7 @@
       <c r="E10" s="20" t="s">
         <v>282</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="112"/>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -9607,7 +9955,7 @@
       <c r="E11" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="F11" s="108"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
@@ -9625,7 +9973,7 @@
       <c r="E12" s="20" t="s">
         <v>266</v>
       </c>
-      <c r="F12" s="108"/>
+      <c r="F12" s="112"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B13" s="9"/>
@@ -9647,8 +9995,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="112" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="112" t="s">
+    <row r="16" spans="1:6" s="116" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="116" t="s">
         <v>260</v>
       </c>
     </row>
@@ -9717,7 +10065,7 @@
       <c r="E2" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="F2" s="108" t="s">
+      <c r="F2" s="112" t="s">
         <v>465</v>
       </c>
     </row>
@@ -9737,7 +10085,7 @@
       <c r="E3" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="F3" s="108"/>
+      <c r="F3" s="112"/>
     </row>
     <row r="4" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
@@ -9755,7 +10103,7 @@
       <c r="E4" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="F4" s="108"/>
+      <c r="F4" s="112"/>
     </row>
     <row r="5" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
@@ -9773,7 +10121,7 @@
       <c r="E5" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F5" s="108"/>
+      <c r="F5" s="112"/>
     </row>
     <row r="6" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
@@ -9791,7 +10139,7 @@
       <c r="E6" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F6" s="108"/>
+      <c r="F6" s="112"/>
     </row>
     <row r="7" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
@@ -9809,7 +10157,7 @@
       <c r="E7" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="108"/>
+      <c r="F7" s="112"/>
     </row>
     <row r="8" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
@@ -9827,7 +10175,7 @@
       <c r="E8" s="20" t="s">
         <v>244</v>
       </c>
-      <c r="F8" s="108"/>
+      <c r="F8" s="112"/>
     </row>
     <row r="9" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="8" t="s">
@@ -9845,7 +10193,7 @@
       <c r="E9" s="20">
         <v>0</v>
       </c>
-      <c r="F9" s="108"/>
+      <c r="F9" s="112"/>
     </row>
     <row r="10" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
@@ -9863,7 +10211,7 @@
       <c r="E10" s="20">
         <v>0</v>
       </c>
-      <c r="F10" s="108"/>
+      <c r="F10" s="112"/>
     </row>
     <row r="11" spans="1:6" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
@@ -9881,7 +10229,7 @@
       <c r="E11" s="20">
         <v>0</v>
       </c>
-      <c r="F11" s="108"/>
+      <c r="F11" s="112"/>
     </row>
     <row r="12" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A12" s="8" t="s">
@@ -9899,7 +10247,7 @@
       <c r="E12" s="20">
         <v>0</v>
       </c>
-      <c r="F12" s="108"/>
+      <c r="F12" s="112"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
@@ -9922,8 +10270,8 @@
         <v>229</v>
       </c>
     </row>
-    <row r="16" spans="1:6" s="112" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="112" t="s">
+    <row r="16" spans="1:6" s="116" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="116" t="s">
         <v>260</v>
       </c>
     </row>
